--- a/intermidiate_tables_csv/05_summary_table.xlsx
+++ b/intermidiate_tables_csv/05_summary_table.xlsx
@@ -448,40 +448,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.648</v>
+        <v>0.644105222734255</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04381780460041327</v>
+        <v>0.05196825198558619</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Random Feature Selection</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.636</v>
+        <v>0.6400089605734767</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02880972058177589</v>
+        <v>0.05871344425959124</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Random Feature Selection</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.634</v>
+        <v>0.6341205837173579</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04037325847637269</v>
+        <v>0.03320817943586356</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.62</v>
+        <v>0.6340885816692269</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03316624790355403</v>
+        <v>0.06336994746619377</v>
       </c>
     </row>
   </sheetData>

--- a/intermidiate_tables_csv/05_summary_table.xlsx
+++ b/intermidiate_tables_csv/05_summary_table.xlsx
@@ -448,40 +448,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.644105222734255</v>
+        <v>0.6881720430107527</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05196825198558619</v>
+        <v>0.06024309334484235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Random Feature Selection</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6400089605734767</v>
+        <v>0.6720430107526882</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05871344425959124</v>
+        <v>0.03022015996233576</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Random Feature Selection</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6341205837173579</v>
+        <v>0.6701228878648233</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03320817943586356</v>
+        <v>0.06158001899937528</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6340885816692269</v>
+        <v>0.6680747567844343</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06336994746619377</v>
+        <v>0.05069383019776282</v>
       </c>
     </row>
   </sheetData>

--- a/intermidiate_tables_csv/05_summary_table.xlsx
+++ b/intermidiate_tables_csv/05_summary_table.xlsx
@@ -448,40 +448,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.644105222734255</v>
+        <v>0.6740271377368152</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05196825198558619</v>
+        <v>0.05412530480754549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Random Feature Selection</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6400089605734767</v>
+        <v>0.6599462365591399</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05871344425959124</v>
+        <v>0.07603652771268088</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Random Feature Selection</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6341205837173579</v>
+        <v>0.6559779825908858</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03320817943586356</v>
+        <v>0.04313916785692158</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6340885816692269</v>
+        <v>0.6539938556067588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06336994746619377</v>
+        <v>0.06708997175282827</v>
       </c>
     </row>
   </sheetData>
